--- a/外网端源码/交接班日志空模板.xlsx
+++ b/外网端源码/交接班日志空模板.xlsx
@@ -405,10 +405,10 @@
     <t>双方班组签字确认清楚知道以上信息</t>
   </si>
   <si>
-    <t>交班值班长签字</t>
-  </si>
-  <si>
-    <t>接班值班长签字</t>
+    <t>交班人</t>
+  </si>
+  <si>
+    <t>接班人</t>
   </si>
   <si>
     <t>审核人：</t>
@@ -3262,7 +3262,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{632b9989-5af6-46f0-b6ac-3c61f14067ce}</x14:id>
+          <x14:id>{1bf9c524-cf30-4694-9a6c-8d7a0d4b90f5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3284,7 +3284,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{632b9989-5af6-46f0-b6ac-3c61f14067ce}">
+          <x14:cfRule type="dataBar" id="{1bf9c524-cf30-4694-9a6c-8d7a0d4b90f5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" direction="leftToRight">
               <x14:cfvo type="num">
                 <xm:f>1</xm:f>

--- a/外网端源码/交接班日志空模板.xlsx
+++ b/外网端源码/交接班日志空模板.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>数据中心交接班日志</t>
   </si>
@@ -2129,7 +2129,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns2="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2301,7 +2301,9 @@
       <c r="E10" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="29"/>
+      <c r="F10" s="29">
+        <v>15</v>
+      </c>
       <c r="G10" s="30"/>
       <c r="H10" s="31"/>
       <c r="I10" s="3"/>
@@ -2708,14 +2710,14 @@
       <c r="B33" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="F33" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
       <c r="G33" s="14"/>
       <c r="H33" s="14" t="s">
         <v>68</v>
@@ -2729,14 +2731,14 @@
       <c r="B34" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C34" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="F34" s="40" t="s">
+        <v>58</v>
+      </c>
       <c r="G34" s="41"/>
       <c r="H34" s="41" t="s">
         <v>58</v>
@@ -3181,7 +3183,7 @@
       <c r="I59" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="72">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:H2"/>
@@ -3217,8 +3219,6 @@
     <mergeCell ref="D30:G30"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="A32:H32"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D34:G34"/>
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="F37:G37"/>
@@ -3252,6 +3252,10 @@
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A51:A55"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="F34:G34"/>
   </mergeCells>
   <conditionalFormatting sqref="D10">
     <cfRule type="dataBar" priority="1">
@@ -3261,8 +3265,8 @@
         <color theme="9"/>
       </dataBar>
       <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1bf9c524-cf30-4694-9a6c-8d7a0d4b90f5}</x14:id>
+        <ext uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <ns1:id>{1bf9c524-cf30-4694-9a6c-8d7a0d4b90f5}</ns1:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3281,25 +3285,25 @@
   <pageSetup paperSize="9" scale="79" orientation="landscape"/>
   <headerFooter/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1bf9c524-cf30-4694-9a6c-8d7a0d4b90f5}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" direction="leftToRight">
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>15264</xm:f>
-              </x14:cfvo>
-              <x14:borderColor theme="9" tint="-0.249977111117893"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>D10</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
+    <ext uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <ns1:conditionalFormattings>
+        <ns1:conditionalFormatting>
+          <ns1:cfRule type="dataBar" id="{1bf9c524-cf30-4694-9a6c-8d7a0d4b90f5}">
+            <ns1:dataBar minLength="0" maxLength="100" border="1" direction="leftToRight">
+              <ns1:cfvo type="num">
+                <ns2:f>1</ns2:f>
+              </ns1:cfvo>
+              <ns1:cfvo type="num">
+                <ns2:f>15264</ns2:f>
+              </ns1:cfvo>
+              <ns1:borderColor theme="9" tint="-0.249977111117893"/>
+              <ns1:negativeFillColor rgb="FFFF0000"/>
+              <ns1:axisColor rgb="FF000000"/>
+            </ns1:dataBar>
+          </ns1:cfRule>
+          <ns2:sqref>D10</ns2:sqref>
+        </ns1:conditionalFormatting>
+      </ns1:conditionalFormattings>
     </ext>
   </extLst>
 </worksheet>

--- a/外网端源码/交接班日志空模板.xlsx
+++ b/外网端源码/交接班日志空模板.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="127">
   <si>
     <t>数据中心交接班日志</t>
   </si>
@@ -1320,10 +1320,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1422,7 +1422,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2129,7 +2129,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns2="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3219,6 +3219,10 @@
     <mergeCell ref="D30:G30"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="A32:H32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="F34:G34"/>
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="F37:G37"/>
@@ -3252,10 +3256,6 @@
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A51:A55"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="F34:G34"/>
   </mergeCells>
   <conditionalFormatting sqref="D10">
     <cfRule type="dataBar" priority="1">
@@ -3265,8 +3265,8 @@
         <color theme="9"/>
       </dataBar>
       <extLst>
-        <ext uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <ns1:id>{1bf9c524-cf30-4694-9a6c-8d7a0d4b90f5}</ns1:id>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{ffac678d-f27e-49bf-aa41-07a65a8c877c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3285,25 +3285,25 @@
   <pageSetup paperSize="9" scale="79" orientation="landscape"/>
   <headerFooter/>
   <extLst>
-    <ext uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <ns1:conditionalFormattings>
-        <ns1:conditionalFormatting>
-          <ns1:cfRule type="dataBar" id="{1bf9c524-cf30-4694-9a6c-8d7a0d4b90f5}">
-            <ns1:dataBar minLength="0" maxLength="100" border="1" direction="leftToRight">
-              <ns1:cfvo type="num">
-                <ns2:f>1</ns2:f>
-              </ns1:cfvo>
-              <ns1:cfvo type="num">
-                <ns2:f>15264</ns2:f>
-              </ns1:cfvo>
-              <ns1:borderColor theme="9" tint="-0.249977111117893"/>
-              <ns1:negativeFillColor rgb="FFFF0000"/>
-              <ns1:axisColor rgb="FF000000"/>
-            </ns1:dataBar>
-          </ns1:cfRule>
-          <ns2:sqref>D10</ns2:sqref>
-        </ns1:conditionalFormatting>
-      </ns1:conditionalFormattings>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{ffac678d-f27e-49bf-aa41-07a65a8c877c}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" direction="leftToRight">
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>15264</xm:f>
+              </x14:cfvo>
+              <x14:borderColor theme="9" tint="-0.249977111117893"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D10</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
     </ext>
   </extLst>
 </worksheet>
